--- a/docs/legal-pages-information.xlsx
+++ b/docs/legal-pages-information.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD984AB-C305-4619-8918-832D7D403E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F620FFAE-F448-4C00-99F8-7B74758FC67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="98">
   <si>
     <t>FindMyRobo — information needed to write the legal pages</t>
   </si>
@@ -288,13 +288,34 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Within 45 days of receiving the returned item</t>
+  </si>
+  <si>
+    <t>Intallation and demo services</t>
+  </si>
+  <si>
+    <t>1 year</t>
+  </si>
+  <si>
+    <t>3-7 business days</t>
+  </si>
+  <si>
+    <t>Warranty repair</t>
+  </si>
+  <si>
+    <t>Phone call after the installation is requested on the website.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,6 +362,12 @@
       <sz val="9"/>
       <color rgb="FF666666"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -406,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -429,6 +456,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -436,8 +466,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -790,34 +820,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="3" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -892,7 +922,7 @@
       <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="8">
         <v>125563010022</v>
       </c>
       <c r="F8" s="7" t="s">
@@ -912,7 +942,7 @@
       <c r="D9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="8">
         <v>125563010022</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -973,7 +1003,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>26</v>
@@ -993,7 +1023,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>29</v>
@@ -1013,7 +1043,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>31</v>
@@ -1073,7 +1103,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>38</v>
@@ -1092,9 +1122,7 @@
       <c r="D18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>11</v>
-      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="7" t="s">
         <v>40</v>
       </c>
@@ -1112,7 +1140,9 @@
       <c r="D19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="F19" s="7" t="s">
         <v>42</v>
       </c>
@@ -1131,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>44</v>
@@ -1170,8 +1200,8 @@
       <c r="D22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="6">
-        <v>5</v>
+      <c r="E22" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>50</v>
@@ -1211,7 +1241,7 @@
         <v>55</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>56</v>
@@ -1231,7 +1261,7 @@
         <v>59</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>60</v>
@@ -1251,7 +1281,7 @@
         <v>62</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>63</v>
@@ -1290,7 +1320,9 @@
       <c r="D28" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="6"/>
+      <c r="E28" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="F28" s="7" t="s">
         <v>11</v>
       </c>
@@ -1309,7 +1341,7 @@
         <v>70</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>71</v>
@@ -1329,7 +1361,7 @@
         <v>73</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>11</v>
@@ -1349,7 +1381,7 @@
         <v>75</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>76</v>
@@ -1369,7 +1401,7 @@
         <v>78</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>11</v>
@@ -1389,7 +1421,7 @@
         <v>80</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>11</v>
@@ -1409,7 +1441,7 @@
         <v>82</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>11</v>
@@ -1429,7 +1461,7 @@
         <v>84</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>11</v>
@@ -1449,7 +1481,7 @@
         <v>86</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>11</v>
@@ -1462,6 +1494,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
